--- a/journal_analyzer/kyungnam/감사조서/Kyungnam_mapping_list_25년.xlsx
+++ b/journal_analyzer/kyungnam/감사조서/Kyungnam_mapping_list_25년.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_부채_미지급금거래처</t>
+          <t>부채_미지급금거래처</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_부채_미지급금사원</t>
+          <t>부채_미지급금사원</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_부채_미지급비용급여</t>
+          <t>부채_미지급비용급여</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_부채_미지급비용신용카드</t>
+          <t>부채_미지급비용신용카드</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_부채_미지급비용이자</t>
+          <t>부채_미지급비용이자</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_부채_일반선수금</t>
+          <t>부채_일반선수금</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_급료와임금급여판관</t>
+          <t>비용_급료와임금급여판관</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_급료와임금연차수당판관</t>
+          <t>비용_급료와임금연차수당판관</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_상여금인센티브판관</t>
+          <t>비용_상여금인센티브판관</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_급여급료제조</t>
+          <t>비용_급여급료제조</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_급여급료제조의령</t>
+          <t>비용_급여급료제조의령</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_급여기타제조</t>
+          <t>비용_급여기타제조</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_급여연월차제조</t>
+          <t>비용_급여연월차제조</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>총계정원장_비용_상여금제조</t>
+          <t>비용_상여금제조</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>상세거래_투자부동산토지_차변</t>
+          <t>투자부동산토지_차</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>상세거래_투자부동산건물_차변</t>
+          <t>투자부동산건물_차</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>상세거래_투자부동산건설중인자산_차변</t>
+          <t>투자부동산건설중인자산_차</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>상세거래_투자부동산토지_대변</t>
+          <t>투자부동산토지_대</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>상세거래_투자부동산건물_대변</t>
+          <t>투자부동산건물_대</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>상세거래_투자부동산건설중인자산_대변</t>
+          <t>투자부동산건설중인자산_대</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>상세거래_토지_차변</t>
+          <t>토지_차</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>상세거래_건물_차변</t>
+          <t>건물_차</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>상세거래_구축물_차변</t>
+          <t>구축물_차</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>상세거래_차량운반구_차변</t>
+          <t>차량운반구_차</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>상세거래_기계장치_차변</t>
+          <t>기계장치_차</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>상세거래_시설장치_차변</t>
+          <t>시설장치_차</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>상세거래_건설중인자산_차변</t>
+          <t>건설중인자산_차</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>상세거래_기타의무형자산_차변</t>
+          <t>기타의무형자산_차</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>상세거래_토지_대변</t>
+          <t>토지_대</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>상세거래_건물_대변</t>
+          <t>건물_대</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>상세거래_차량운반구_대변</t>
+          <t>차량운반구_대</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>상세거래_시설장치_대변</t>
+          <t>시설장치_대</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>상세거래_건설중인자산_대변</t>
+          <t>건설중인자산_대</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>상세거래_기타의무형자산_대변</t>
+          <t>기타의무형자산_대</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>상세거래_보증금임차보증금_차변</t>
+          <t>보증금임차보증금_차</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>상세거래_보증금임차보증금_대변</t>
+          <t>보증금임차보증금_대</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>상세거래_퇴직급여충당금_차변</t>
+          <t>퇴직급여충당금_차</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>상세거래_퇴직급여충당금_대변</t>
+          <t>퇴직급여충당금_대</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>상세거래_퇴직연금예치금_차변</t>
+          <t>퇴직연금예치금_차</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>상세거래_퇴직연금예치금_대변</t>
+          <t>퇴직연금예치금_대</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>상세거래_임대보증금_대변</t>
+          <t>임대보증금_대</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>상세거래_임대보증금(비유동)_대변</t>
+          <t>임대보증금비유동_대</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>상세거래_장기미지급비용_대변</t>
+          <t>장기미지급비용_대</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>데이터개요_계정별</t>
+          <t>계정별</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>AI검토결과</t>
+          <t>결과</t>
         </is>
       </c>
       <c r="D46" s="7" t="n"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>AI검토_확인전표</t>
+          <t>확인전표</t>
         </is>
       </c>
       <c r="D47" s="7" t="n"/>

--- a/journal_analyzer/kyungnam/감사조서/Kyungnam_mapping_list_25년.xlsx
+++ b/journal_analyzer/kyungnam/감사조서/Kyungnam_mapping_list_25년.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>부채_미지급금거래처</t>
+          <t>21_총계정원장_부채_미지급금거래처</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>부채_미지급금사원</t>
+          <t>21_총계정원장_부채_미지급금사원</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>부채_미지급비용급여</t>
+          <t>21_총계정원장_부채_미지급비용급여</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>부채_미지급비용신용카드</t>
+          <t>21_총계정원장_부채_미지급비용신용카드</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>부채_미지급비용이자</t>
+          <t>21_총계정원장_부채_미지급비용이자</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>부채_일반선수금</t>
+          <t>21_총계정원장_부채_일반선수금</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>비용_급료와임금급여판관</t>
+          <t>21_총계정원장_비용_급료와임금급여판관</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>비용_급료와임금연차수당판관</t>
+          <t>21_총계정원장_비용_급료와임금연차수당판관</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>비용_상여금인센티브판관</t>
+          <t>21_총계정원장_비용_상여금인센티브판관</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>비용_급여급료제조</t>
+          <t>21_총계정원장_비용_급여급료제조</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>비용_급여급료제조의령</t>
+          <t>21_총계정원장_비용_급여급료제조의령</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>비용_급여기타제조</t>
+          <t>21_총계정원장_비용_급여기타제조</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>비용_급여연월차제조</t>
+          <t>21_총계정원장_비용_급여연월차제조</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>비용_상여금제조</t>
+          <t>21_총계정원장_비용_상여금제조</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>투자부동산토지_차</t>
+          <t>23_계정별 상세거래내역_투자부동산토지_차</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>투자부동산건물_차</t>
+          <t>23_계정별 상세거래내역_투자부동산건물_차</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>투자부동산건설중인자산_차</t>
+          <t>23_계정별 상세거래내역_투자부동산건설중인자산_차</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>투자부동산토지_대</t>
+          <t>23_계정별 상세거래내역_투자부동산토지_대</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>투자부동산건물_대</t>
+          <t>23_계정별 상세거래내역_투자부동산건물_대</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>투자부동산건설중인자산_대</t>
+          <t>23_계정별 상세거래내역_투자부동산건설중인자산_대</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>토지_차</t>
+          <t>23_계정별 상세거래내역_토지_차</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>건물_차</t>
+          <t>23_계정별 상세거래내역_건물_차</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>구축물_차</t>
+          <t>23_계정별 상세거래내역_구축물_차</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>차량운반구_차</t>
+          <t>23_계정별 상세거래내역_차량운반구_차</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>기계장치_차</t>
+          <t>23_계정별 상세거래내역_기계장치_차</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>시설장치_차</t>
+          <t>23_계정별 상세거래내역_시설장치_차</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>건설중인자산_차</t>
+          <t>23_계정별 상세거래내역_건설중인자산_차</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>기타의무형자산_차</t>
+          <t>23_계정별 상세거래내역_기타의무형자산_차</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>토지_대</t>
+          <t>23_계정별 상세거래내역_토지_대</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>건물_대</t>
+          <t>23_계정별 상세거래내역_건물_대</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>차량운반구_대</t>
+          <t>23_계정별 상세거래내역_차량운반구_대</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>시설장치_대</t>
+          <t>23_계정별 상세거래내역_시설장치_대</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>건설중인자산_대</t>
+          <t>23_계정별 상세거래내역_건설중인자산_대</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>기타의무형자산_대</t>
+          <t>23_계정별 상세거래내역_기타의무형자산_대</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>보증금임차보증금_차</t>
+          <t>23_계정별 상세거래내역_보증금임차보증금_차</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>보증금임차보증금_대</t>
+          <t>23_계정별 상세거래내역_보증금임차보증금_대</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>퇴직급여충당금_차</t>
+          <t>23_계정별 상세거래내역_퇴직급여충당금_차</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>퇴직급여충당금_대</t>
+          <t>23_계정별 상세거래내역_퇴직급여충당금_대</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>퇴직연금예치금_차</t>
+          <t>23_계정별 상세거래내역_퇴직연금예치금_차</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>퇴직연금예치금_대</t>
+          <t>23_계정별 상세거래내역_퇴직연금예치금_대</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>임대보증금_대</t>
+          <t>23_계정별 상세거래내역_임대보증금_대</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>임대보증금비유동_대</t>
+          <t>23_계정별 상세거래내역_임대보증금비유동_대</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>장기미지급비용_대</t>
+          <t>23_계정별 상세거래내역_장기미지급비용_대</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>계정별</t>
+          <t>04_데이터 개요_계정별</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>결과</t>
+          <t>26_AI계정별분석_실행_결과</t>
         </is>
       </c>
       <c r="D46" s="7" t="n"/>

--- a/journal_analyzer/kyungnam/감사조서/Kyungnam_mapping_list_25년.xlsx
+++ b/journal_analyzer/kyungnam/감사조서/Kyungnam_mapping_list_25년.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col width="23.25" customWidth="1" style="15" min="1" max="1"/>
@@ -2428,45 +2428,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>AI검토_확인전표(보통예금)</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>분석결과_kyungnam</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>확인전표</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>당기_Kyungnam_조서_26년</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="inlineStr">
-        <is>
-          <t>AI검토</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="n"/>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>AI_INJECT</t>
-        </is>
-      </c>
-    </row>
+    <row r="47" ht="17" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
